--- a/entity_report.xlsx
+++ b/entity_report.xlsx
@@ -41,7 +41,7 @@
     <t>icici</t>
   </si>
   <si>
-    <t>CAEBBD0D</t>
+    <t>4CFA9978</t>
   </si>
   <si>
     <t>REPOSITORY_NAME</t>
@@ -50,7 +50,7 @@
     <t>ICICI-BANK-LOAN-PLATFORM</t>
   </si>
   <si>
-    <t>83C3D905</t>
+    <t>9241AB07</t>
   </si>
   <si>
     <t>COMPANY_BRAND</t>
@@ -1663,19 +1663,19 @@
     <t>sql/schema.sql</t>
   </si>
   <si>
-    <t>src/main/java/com/CAEBBD0D/loan/AuthService.java</t>
-  </si>
-  <si>
-    <t>src/main/java/com/CAEBBD0D/loan/CustomerService.java</t>
-  </si>
-  <si>
-    <t>src/main/java/com/CAEBBD0D/loan/LoanController.java</t>
-  </si>
-  <si>
-    <t>src/main/java/com/CAEBBD0D/loan/LoanService.java</t>
-  </si>
-  <si>
-    <t>src/main/java/com/CAEBBD0D/loan/PaymentService.java</t>
+    <t>src/main/java/com/4CFA9978/loan/AuthService.java</t>
+  </si>
+  <si>
+    <t>src/main/java/com/4CFA9978/loan/CustomerService.java</t>
+  </si>
+  <si>
+    <t>src/main/java/com/4CFA9978/loan/LoanController.java</t>
+  </si>
+  <si>
+    <t>src/main/java/com/4CFA9978/loan/LoanService.java</t>
+  </si>
+  <si>
+    <t>src/main/java/com/4CFA9978/loan/PaymentService.java</t>
   </si>
   <si>
     <t>https://internal.icici.com/loan-api/v1/payments/webhook</t>
@@ -1802,7 +1802,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.65234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.08984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="101.58984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="113.8203125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="9.61328125" customWidth="true" bestFit="true"/>
